--- a/tables/table-1.xlsx
+++ b/tables/table-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="285" documentId="8_{A016B768-059C-4773-BFB7-E0E6207DCD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04A0D37A-8070-46AE-8AE5-1A3DDBEAD9BB}"/>
+  <xr:revisionPtr revIDLastSave="582" documentId="8_{A016B768-059C-4773-BFB7-E0E6207DCD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF23816-8081-4EF1-BE30-FE4B4A90417B}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4D26BEB4-BA8B-4CD5-932F-2328E7569F99}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="162">
   <si>
     <t>Species Name</t>
   </si>
@@ -356,41 +356,183 @@
     <t>229x229x3</t>
   </si>
   <si>
-    <t>145 m 49 s</t>
-  </si>
-  <si>
-    <t>158 m 34 s</t>
-  </si>
-  <si>
-    <t>37 m 10 s</t>
-  </si>
-  <si>
-    <t>87 m 24 s</t>
-  </si>
-  <si>
-    <t>23 m 47 s</t>
-  </si>
-  <si>
-    <t>54 m 19 s</t>
-  </si>
-  <si>
-    <t>299 m 8 s</t>
-  </si>
-  <si>
-    <t>55 m 4 s</t>
-  </si>
-  <si>
     <t>Input Size (px)</t>
+  </si>
+  <si>
+    <t>Baseline</t>
+  </si>
+  <si>
+    <t>Cutmix</t>
+  </si>
+  <si>
+    <t>Improvement</t>
+  </si>
+  <si>
+    <t>Table: CutMix Augmentation Results</t>
+  </si>
+  <si>
+    <t>+ 0.4%</t>
+  </si>
+  <si>
+    <t>- 0.8%</t>
+  </si>
+  <si>
+    <t>+ 2.0%</t>
+  </si>
+  <si>
+    <t>+ 1.2%</t>
+  </si>
+  <si>
+    <t>Total Confused Pairs</t>
+  </si>
+  <si>
+    <t>3 h 0 min 3 s</t>
+  </si>
+  <si>
+    <t>14 min 1 s</t>
+  </si>
+  <si>
+    <t>16 min 57 s</t>
+  </si>
+  <si>
+    <t>145 min 49 s</t>
+  </si>
+  <si>
+    <t>158 min 34 s</t>
+  </si>
+  <si>
+    <t>37 min 10 s</t>
+  </si>
+  <si>
+    <t>87 min 24 s</t>
+  </si>
+  <si>
+    <t>23 min 47 s</t>
+  </si>
+  <si>
+    <t>54 min 19 s</t>
+  </si>
+  <si>
+    <t>299 min 8 s</t>
+  </si>
+  <si>
+    <t>55 min 4 s</t>
+  </si>
+  <si>
+    <t>1 h 30 min 14 s</t>
+  </si>
+  <si>
+    <t>Table: Standard Augmentation Results</t>
+  </si>
+  <si>
+    <t>Standard Augmentations</t>
+  </si>
+  <si>
+    <t>14 min 44 s</t>
+  </si>
+  <si>
+    <t>16 min 40 s</t>
+  </si>
+  <si>
+    <t>3 h 9 min 42 s</t>
+  </si>
+  <si>
+    <t>1 h 42 min 30 s</t>
+  </si>
+  <si>
+    <t>- 0.4%</t>
+  </si>
+  <si>
+    <t>Table: Targeted Augmentation Results</t>
+  </si>
+  <si>
+    <t>Targeted Augmentations</t>
+  </si>
+  <si>
+    <t>44 min 20 s</t>
+  </si>
+  <si>
+    <t>40 min 54 s</t>
+  </si>
+  <si>
+    <t>7 h 1 min 27 s</t>
+  </si>
+  <si>
+    <t>3 h 16 min 55 s</t>
+  </si>
+  <si>
+    <t>- 2.8%</t>
+  </si>
+  <si>
+    <t>Table: Final Fine-Tuning Results</t>
+  </si>
+  <si>
+    <t>3.4M</t>
+  </si>
+  <si>
+    <t>1.3M</t>
+  </si>
+  <si>
+    <t>28.4M</t>
+  </si>
+  <si>
+    <t>12.6M</t>
+  </si>
+  <si>
+    <t>features[5,6,7] &amp; classifier</t>
+  </si>
+  <si>
+    <t>features[16,17,18] &amp; classifier</t>
+  </si>
+  <si>
+    <t>serial_blocks4[4,5,6,7] &amp; norm4 &amp; head</t>
+  </si>
+  <si>
+    <t>Test Accuracy</t>
+  </si>
+  <si>
+    <t>3 h 22 min 9 s</t>
+  </si>
+  <si>
+    <t>2 h 35 min 43 s</t>
+  </si>
+  <si>
+    <t>22 h 35 min 14 s</t>
+  </si>
+  <si>
+    <t>14 h 43 min 5 s</t>
+  </si>
+  <si>
+    <t>Table: Complete Optimisation Results</t>
+  </si>
+  <si>
+    <t>+ CutMix</t>
+  </si>
+  <si>
+    <t>+ Fine-Tuning</t>
+  </si>
+  <si>
+    <t>Total Improvement</t>
+  </si>
+  <si>
+    <t>+ Standard Augmentations</t>
+  </si>
+  <si>
+    <t>+ Targeted Augmentations</t>
+  </si>
+  <si>
+    <t>+ 2.8%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +585,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FFD4D4D4"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -452,7 +607,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -552,11 +707,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -583,10 +761,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -596,9 +774,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -607,7 +782,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -622,10 +797,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -634,13 +806,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -649,33 +821,123 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="9" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="8">
     <dxf>
@@ -1188,7 +1450,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE05A1F3-5367-4D87-8E13-238A620B94D7}">
-  <dimension ref="A1:W53"/>
+  <dimension ref="A1:BO53"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.08984375" customWidth="1"/>
@@ -1209,38 +1471,124 @@
     <col min="21" max="21" width="16.1796875" customWidth="1"/>
     <col min="22" max="22" width="17.26953125" customWidth="1"/>
     <col min="23" max="23" width="12.1796875" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" customWidth="1"/>
+    <col min="26" max="26" width="21.54296875" customWidth="1"/>
+    <col min="27" max="27" width="18.7265625" customWidth="1"/>
+    <col min="28" max="28" width="18.90625" customWidth="1"/>
+    <col min="29" max="29" width="20" customWidth="1"/>
+    <col min="30" max="30" width="13.08984375" customWidth="1"/>
+    <col min="32" max="32" width="16.6328125" customWidth="1"/>
+    <col min="33" max="33" width="9.54296875" customWidth="1"/>
+    <col min="34" max="34" width="22.453125" customWidth="1"/>
+    <col min="35" max="35" width="14.453125" customWidth="1"/>
+    <col min="36" max="36" width="17.90625" customWidth="1"/>
+    <col min="37" max="37" width="13.453125" customWidth="1"/>
+    <col min="39" max="39" width="18.453125" customWidth="1"/>
+    <col min="40" max="40" width="22.26953125" customWidth="1"/>
+    <col min="41" max="41" width="20.453125" customWidth="1"/>
+    <col min="42" max="42" width="15.54296875" customWidth="1"/>
+    <col min="43" max="43" width="17.36328125" customWidth="1"/>
+    <col min="44" max="44" width="15.7265625" customWidth="1"/>
+    <col min="46" max="46" width="17.7265625" customWidth="1"/>
+    <col min="47" max="47" width="22" customWidth="1"/>
+    <col min="48" max="48" width="19.453125" customWidth="1"/>
+    <col min="49" max="49" width="34.453125" customWidth="1"/>
+    <col min="50" max="50" width="15.1796875" customWidth="1"/>
+    <col min="51" max="51" width="16.7265625" customWidth="1"/>
+    <col min="52" max="52" width="15.7265625" customWidth="1"/>
+    <col min="54" max="54" width="17.7265625" customWidth="1"/>
+    <col min="55" max="55" width="19.1796875" customWidth="1"/>
+    <col min="56" max="56" width="22.90625" customWidth="1"/>
+    <col min="57" max="57" width="21.90625" customWidth="1"/>
+    <col min="58" max="59" width="22.90625" customWidth="1"/>
+    <col min="60" max="60" width="15.81640625" customWidth="1"/>
+    <col min="62" max="62" width="25.453125" customWidth="1"/>
+    <col min="63" max="63" width="15.1796875" customWidth="1"/>
+    <col min="64" max="64" width="24.08984375" customWidth="1"/>
+    <col min="65" max="65" width="24.90625" customWidth="1"/>
+    <col min="66" max="66" width="22.453125" customWidth="1"/>
+    <col min="67" max="67" width="23.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:67" x14ac:dyDescent="0.35">
+      <c r="A1" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="H1" s="39" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="67"/>
+      <c r="H1" s="66" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="Q1" s="37" t="s">
+      <c r="I1" s="66"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="66"/>
+      <c r="L1" s="66"/>
+      <c r="M1" s="66"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="66"/>
+      <c r="Q1" s="65" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="37"/>
-      <c r="S1" s="37"/>
-      <c r="T1" s="37"/>
-      <c r="U1" s="37"/>
-      <c r="V1" s="37"/>
-      <c r="W1" s="37"/>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="R1" s="65"/>
+      <c r="S1" s="65"/>
+      <c r="T1" s="65"/>
+      <c r="U1" s="65"/>
+      <c r="V1" s="65"/>
+      <c r="W1" s="65"/>
+      <c r="Y1" s="68" t="s">
+        <v>110</v>
+      </c>
+      <c r="Z1" s="68"/>
+      <c r="AA1" s="68"/>
+      <c r="AB1" s="68"/>
+      <c r="AC1" s="68"/>
+      <c r="AD1" s="68"/>
+      <c r="AF1" s="62" t="s">
+        <v>128</v>
+      </c>
+      <c r="AG1" s="62"/>
+      <c r="AH1" s="62"/>
+      <c r="AI1" s="62"/>
+      <c r="AJ1" s="62"/>
+      <c r="AK1" s="62"/>
+      <c r="AL1" s="39"/>
+      <c r="AM1" s="62" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN1" s="62"/>
+      <c r="AO1" s="62"/>
+      <c r="AP1" s="62"/>
+      <c r="AQ1" s="62"/>
+      <c r="AR1" s="62"/>
+      <c r="AT1" s="63" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU1" s="63"/>
+      <c r="AV1" s="63"/>
+      <c r="AW1" s="63"/>
+      <c r="AX1" s="63"/>
+      <c r="AY1" s="63"/>
+      <c r="AZ1" s="63"/>
+      <c r="BB1" s="63" t="s">
+        <v>155</v>
+      </c>
+      <c r="BC1" s="63"/>
+      <c r="BD1" s="63"/>
+      <c r="BE1" s="63"/>
+      <c r="BF1" s="63"/>
+      <c r="BG1" s="63"/>
+      <c r="BH1" s="63"/>
+      <c r="BJ1" s="64"/>
+      <c r="BK1" s="64"/>
+      <c r="BL1" s="64"/>
+      <c r="BM1" s="64"/>
+      <c r="BN1" s="64"/>
+      <c r="BO1" s="64"/>
+    </row>
+    <row r="2" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>55</v>
       </c>
@@ -1259,53 +1607,155 @@
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="I2" s="16" t="s">
+      <c r="I2" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="J2" s="17" t="s">
+      <c r="J2" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="K2" s="16" t="s">
+      <c r="K2" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="M2" s="17" t="s">
+      <c r="M2" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="N2" s="17" t="s">
+      <c r="N2" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="O2" s="17" t="s">
         <v>62</v>
       </c>
-      <c r="Q2" s="30" t="s">
+      <c r="Q2" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="R2" s="30" t="s">
+      <c r="R2" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="S2" s="31" t="s">
+      <c r="S2" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="31" t="s">
+      <c r="T2" s="29" t="s">
         <v>88</v>
       </c>
-      <c r="U2" s="31" t="s">
+      <c r="U2" s="29" t="s">
         <v>96</v>
       </c>
-      <c r="V2" s="32" t="s">
+      <c r="V2" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="W2" s="30" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="W2" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="Y2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="Z2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA2" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="AB2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="AC2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="AD2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG2" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="AH2" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="AJ2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="AK2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AN2" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO2" s="28" t="s">
+        <v>136</v>
+      </c>
+      <c r="AP2" s="28" t="s">
+        <v>109</v>
+      </c>
+      <c r="AQ2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="AR2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AT2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AU2" s="28" t="s">
+        <v>96</v>
+      </c>
+      <c r="AV2" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="AW2" s="28" t="s">
+        <v>88</v>
+      </c>
+      <c r="AX2" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="AY2" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="AZ2" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="BC2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="BD2" s="58" t="s">
+        <v>156</v>
+      </c>
+      <c r="BE2" s="58" t="s">
+        <v>159</v>
+      </c>
+      <c r="BF2" s="58" t="s">
+        <v>160</v>
+      </c>
+      <c r="BG2" s="58" t="s">
+        <v>157</v>
+      </c>
+      <c r="BH2" s="58" t="s">
+        <v>158</v>
+      </c>
+      <c r="BJ2" s="28"/>
+      <c r="BK2" s="28"/>
+      <c r="BL2" s="58"/>
+      <c r="BM2" s="58"/>
+      <c r="BN2" s="58"/>
+      <c r="BO2" s="58"/>
+    </row>
+    <row r="3" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1328,7 +1778,7 @@
         <v>67</v>
       </c>
       <c r="I3" s="9" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="J3" s="13">
         <v>91.16</v>
@@ -1345,7 +1795,7 @@
       <c r="N3" s="14">
         <v>0.93</v>
       </c>
-      <c r="O3" s="15">
+      <c r="O3" s="11">
         <v>0.93</v>
       </c>
       <c r="Q3" s="11" t="s">
@@ -1363,14 +1813,112 @@
       <c r="U3" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="V3" s="27">
+      <c r="V3" s="25">
         <v>0.126</v>
       </c>
       <c r="W3" s="11" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Y3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z3" s="41">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="AA3" s="42">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AB3" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="AC3" s="40">
+        <v>3</v>
+      </c>
+      <c r="AD3" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="AF3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="AG3" s="42">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AH3" s="42">
+        <v>0.98</v>
+      </c>
+      <c r="AI3" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ3" s="40">
+        <v>5</v>
+      </c>
+      <c r="AK3" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="AM3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN3" s="42">
+        <v>0.98</v>
+      </c>
+      <c r="AO3" s="42">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="AP3" s="43" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ3" s="40">
+        <v>6</v>
+      </c>
+      <c r="AR3" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="AT3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="AU3" s="47" t="s">
+        <v>143</v>
+      </c>
+      <c r="AV3" s="42">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="AW3" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="AX3" s="53">
+        <v>0.996</v>
+      </c>
+      <c r="AY3" s="55">
+        <v>1</v>
+      </c>
+      <c r="AZ3" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="BB3" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="BC3" s="41">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="BD3" s="42">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="BE3" s="42">
+        <v>0.98</v>
+      </c>
+      <c r="BF3" s="42">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="BG3" s="53">
+        <v>0.996</v>
+      </c>
+      <c r="BH3" s="59" t="s">
+        <v>114</v>
+      </c>
+      <c r="BJ3" s="40"/>
+      <c r="BK3" s="46"/>
+    </row>
+    <row r="4" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1393,7 +1941,7 @@
         <v>66</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="J4" s="13">
         <v>94.21</v>
@@ -1410,7 +1958,7 @@
       <c r="N4" s="14">
         <v>0.94</v>
       </c>
-      <c r="O4" s="15">
+      <c r="O4" s="11">
         <v>0.94</v>
       </c>
       <c r="Q4" s="11" t="s">
@@ -1422,20 +1970,117 @@
       <c r="S4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="T4" s="25" t="s">
+      <c r="T4" s="23" t="s">
         <v>90</v>
       </c>
       <c r="U4" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="V4" s="27">
+      <c r="V4" s="25">
         <v>7.3999999999999996E-2</v>
       </c>
       <c r="W4" s="11" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Y4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z4" s="35">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AA4" s="44">
+        <v>0.98</v>
+      </c>
+      <c r="AB4" s="45" t="s">
+        <v>112</v>
+      </c>
+      <c r="AC4" s="11">
+        <v>5</v>
+      </c>
+      <c r="AD4" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="AF4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AG4" s="44">
+        <v>0.98</v>
+      </c>
+      <c r="AH4" s="44">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="AI4" s="45" t="s">
+        <v>114</v>
+      </c>
+      <c r="AJ4" s="11">
+        <v>2</v>
+      </c>
+      <c r="AK4" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="AM4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AN4" s="44">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="AO4" s="44">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AP4" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ4" s="11">
+        <v>3</v>
+      </c>
+      <c r="AR4" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="AT4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AU4" s="48" t="s">
+        <v>144</v>
+      </c>
+      <c r="AV4" s="44">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="AW4" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="AX4" s="25">
+        <v>1</v>
+      </c>
+      <c r="AY4" s="56">
+        <v>0</v>
+      </c>
+      <c r="AZ4" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="BB4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="BC4" s="35">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="BD4" s="44">
+        <v>0.98</v>
+      </c>
+      <c r="BE4" s="44">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="BF4" s="44">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="BG4" s="25">
+        <v>1</v>
+      </c>
+      <c r="BH4" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="BJ4" s="11"/>
+    </row>
+    <row r="5" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1458,7 +2103,7 @@
         <v>64</v>
       </c>
       <c r="I5" s="9" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="J5" s="13">
         <v>96.49</v>
@@ -1475,7 +2120,7 @@
       <c r="N5" s="14">
         <v>0.96</v>
       </c>
-      <c r="O5" s="15">
+      <c r="O5" s="11">
         <v>0.96</v>
       </c>
       <c r="Q5" s="11" t="s">
@@ -1487,20 +2132,117 @@
       <c r="S5" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="T5" s="25" t="s">
+      <c r="T5" s="23" t="s">
         <v>91</v>
       </c>
       <c r="U5" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="V5" s="27">
+      <c r="V5" s="25">
         <v>0.193</v>
       </c>
       <c r="W5" s="11" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Y5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z5" s="35">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="AA5" s="44">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="AB5" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="AC5" s="11">
+        <v>2</v>
+      </c>
+      <c r="AD5" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="AF5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AG5" s="44">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="AH5" s="44">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AI5" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="AJ5" s="11">
+        <v>3</v>
+      </c>
+      <c r="AK5" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="AM5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AN5" s="44">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AO5" s="44">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="AP5" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="AQ5" s="11">
+        <v>1</v>
+      </c>
+      <c r="AR5" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="AT5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="AU5" s="48" t="s">
+        <v>145</v>
+      </c>
+      <c r="AV5" s="44">
+        <v>0.33100000000000002</v>
+      </c>
+      <c r="AW5" s="51" t="s">
+        <v>148</v>
+      </c>
+      <c r="AX5" s="25">
+        <v>1</v>
+      </c>
+      <c r="AY5" s="56">
+        <v>0</v>
+      </c>
+      <c r="AZ5" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="BB5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="BC5" s="35">
+        <v>0.97199999999999998</v>
+      </c>
+      <c r="BD5" s="44">
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="BE5" s="44">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="BF5" s="44">
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="BG5" s="25">
+        <v>1</v>
+      </c>
+      <c r="BH5" s="60" t="s">
+        <v>161</v>
+      </c>
+      <c r="BJ5" s="11"/>
+    </row>
+    <row r="6" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1523,7 +2265,7 @@
         <v>71</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="J6" s="13">
         <v>98.2</v>
@@ -1540,7 +2282,7 @@
       <c r="N6" s="14">
         <v>0.97</v>
       </c>
-      <c r="O6" s="15">
+      <c r="O6" s="11">
         <v>0.97</v>
       </c>
       <c r="Q6" s="11" t="s">
@@ -1552,20 +2294,117 @@
       <c r="S6" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="T6" s="25" t="s">
+      <c r="T6" s="23" t="s">
         <v>92</v>
       </c>
       <c r="U6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="V6" s="27">
+      <c r="V6" s="25">
         <v>0.11700000000000001</v>
       </c>
       <c r="W6" s="11" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Y6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z6" s="36">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="AA6" s="37">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AB6" s="38" t="s">
+        <v>114</v>
+      </c>
+      <c r="AC6" s="22">
+        <v>3</v>
+      </c>
+      <c r="AD6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AF6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="AG6" s="37">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="AH6" s="37">
+        <v>0.98</v>
+      </c>
+      <c r="AI6" s="38" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ6" s="22">
+        <v>5</v>
+      </c>
+      <c r="AK6" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="AN6" s="37">
+        <v>0.98</v>
+      </c>
+      <c r="AO6" s="37">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="AP6" s="38" t="s">
+        <v>141</v>
+      </c>
+      <c r="AQ6" s="22">
+        <v>7</v>
+      </c>
+      <c r="AR6" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="AT6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU6" s="49" t="s">
+        <v>146</v>
+      </c>
+      <c r="AV6" s="37">
+        <v>0.28699999999999998</v>
+      </c>
+      <c r="AW6" s="52" t="s">
+        <v>149</v>
+      </c>
+      <c r="AX6" s="54">
+        <v>0.996</v>
+      </c>
+      <c r="AY6" s="57">
+        <v>1</v>
+      </c>
+      <c r="AZ6" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="BB6" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="BC6" s="36">
+        <v>0.97599999999999998</v>
+      </c>
+      <c r="BD6" s="37">
+        <v>0.98799999999999999</v>
+      </c>
+      <c r="BE6" s="37">
+        <v>0.98</v>
+      </c>
+      <c r="BF6" s="37">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="BG6" s="54">
+        <v>0.996</v>
+      </c>
+      <c r="BH6" s="61" t="s">
+        <v>113</v>
+      </c>
+      <c r="BJ6" s="22"/>
+    </row>
+    <row r="7" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1588,7 +2427,7 @@
         <v>65</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="J7" s="13">
         <v>97.58</v>
@@ -1605,32 +2444,38 @@
       <c r="N7" s="14">
         <v>0.98</v>
       </c>
-      <c r="O7" s="15">
+      <c r="O7" s="11">
         <v>0.98</v>
       </c>
-      <c r="Q7" s="15" t="s">
+      <c r="Q7" s="11" t="s">
         <v>68</v>
       </c>
       <c r="R7" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="S7" s="24" t="s">
+      <c r="S7" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="T7" s="25" t="s">
+      <c r="T7" s="23" t="s">
         <v>93</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="V7" s="29">
+      <c r="V7" s="27">
         <v>0.20799999999999999</v>
       </c>
       <c r="W7" s="11" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="34"/>
+      <c r="AA7" s="34"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="34"/>
+      <c r="AD7" s="34"/>
+    </row>
+    <row r="8" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1653,7 +2498,7 @@
         <v>68</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="J8" s="13">
         <v>98.59</v>
@@ -1670,32 +2515,32 @@
       <c r="N8" s="14">
         <v>0.99</v>
       </c>
-      <c r="O8" s="15">
+      <c r="O8" s="11">
         <v>0.99</v>
       </c>
-      <c r="Q8" s="15" t="s">
+      <c r="Q8" s="11" t="s">
         <v>77</v>
       </c>
       <c r="R8" s="11" t="s">
         <v>79</v>
       </c>
-      <c r="S8" s="24" t="s">
+      <c r="S8" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="T8" s="25" t="s">
+      <c r="T8" s="23" t="s">
         <v>94</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="V8" s="29">
+      <c r="V8" s="27">
         <v>0.248</v>
       </c>
       <c r="W8" s="11" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1718,7 +2563,7 @@
         <v>69</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="J9" s="13">
         <v>97.16</v>
@@ -1735,32 +2580,32 @@
       <c r="N9" s="14">
         <v>0.97</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="11">
         <v>0.97</v>
       </c>
-      <c r="Q9" s="23" t="s">
+      <c r="Q9" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="R9" s="33" t="s">
+      <c r="R9" s="22" t="s">
         <v>79</v>
       </c>
-      <c r="S9" s="34" t="s">
+      <c r="S9" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="T9" s="35" t="s">
+      <c r="T9" s="32" t="s">
         <v>95</v>
       </c>
       <c r="U9" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="V9" s="36">
+      <c r="V9" s="33">
         <v>0.215</v>
       </c>
-      <c r="W9" s="33" t="s">
+      <c r="W9" s="22" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1779,32 +2624,32 @@
       <c r="F10" s="1">
         <v>131</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="20">
+      <c r="I10" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="J10" s="19">
         <v>97.34</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="20">
         <v>96.8</v>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="19">
         <v>97.6</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="21">
         <v>0.98</v>
       </c>
-      <c r="N10" s="22">
+      <c r="N10" s="21">
         <v>0.98</v>
       </c>
-      <c r="O10" s="23">
+      <c r="O10" s="22">
         <v>0.97</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1824,7 +2669,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1846,13 +2691,13 @@
       <c r="H12" s="11"/>
       <c r="I12" s="11"/>
       <c r="J12" s="10"/>
-      <c r="K12" s="26"/>
+      <c r="K12" s="24"/>
       <c r="L12" s="10"/>
       <c r="M12" s="11"/>
       <c r="N12" s="11"/>
-      <c r="O12" s="15"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="O12" s="11"/>
+    </row>
+    <row r="13" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1876,11 +2721,11 @@
       <c r="J13" s="10"/>
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
-      <c r="M13" s="27"/>
+      <c r="M13" s="25"/>
       <c r="N13" s="11"/>
-      <c r="O13" s="15"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="O13" s="11"/>
+    </row>
+    <row r="14" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1904,11 +2749,11 @@
       <c r="J14" s="10"/>
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
-      <c r="M14" s="27"/>
+      <c r="M14" s="25"/>
       <c r="N14" s="11"/>
-      <c r="O14" s="15"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="O14" s="11"/>
+    </row>
+    <row r="15" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1930,13 +2775,13 @@
       <c r="H15" s="11"/>
       <c r="I15" s="11"/>
       <c r="J15" s="10"/>
-      <c r="K15" s="25"/>
+      <c r="K15" s="23"/>
       <c r="L15" s="10"/>
-      <c r="M15" s="27"/>
+      <c r="M15" s="25"/>
       <c r="N15" s="11"/>
-      <c r="O15" s="15"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
+      <c r="O15" s="11"/>
+    </row>
+    <row r="16" spans="1:67" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1958,11 +2803,11 @@
       <c r="H16" s="11"/>
       <c r="I16" s="11"/>
       <c r="J16" s="10"/>
-      <c r="K16" s="25"/>
+      <c r="K16" s="23"/>
       <c r="L16" s="10"/>
-      <c r="M16" s="27"/>
+      <c r="M16" s="25"/>
       <c r="N16" s="11"/>
-      <c r="O16" s="15"/>
+      <c r="O16" s="11"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
@@ -1986,11 +2831,11 @@
       <c r="H17" s="11"/>
       <c r="I17" s="11"/>
       <c r="J17" s="10"/>
-      <c r="K17" s="25"/>
+      <c r="K17" s="23"/>
       <c r="L17" s="10"/>
-      <c r="M17" s="27"/>
+      <c r="M17" s="25"/>
       <c r="N17" s="11"/>
-      <c r="O17" s="15"/>
+      <c r="O17" s="11"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
@@ -2011,12 +2856,12 @@
       <c r="F18" s="1">
         <v>175</v>
       </c>
-      <c r="H18" s="15"/>
+      <c r="H18" s="11"/>
       <c r="I18" s="11"/>
-      <c r="J18" s="24"/>
-      <c r="K18" s="25"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="23"/>
       <c r="L18" s="1"/>
-      <c r="M18" s="28"/>
+      <c r="M18" s="26"/>
       <c r="N18" s="11"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.35">
@@ -2038,12 +2883,12 @@
       <c r="F19" s="1">
         <v>149</v>
       </c>
-      <c r="H19" s="15"/>
+      <c r="H19" s="11"/>
       <c r="I19" s="11"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="25"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="23"/>
       <c r="L19" s="1"/>
-      <c r="M19" s="28"/>
+      <c r="M19" s="26"/>
       <c r="N19" s="11"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.35">
@@ -2065,12 +2910,12 @@
       <c r="F20" s="1">
         <v>141</v>
       </c>
-      <c r="H20" s="15"/>
+      <c r="H20" s="11"/>
       <c r="I20" s="11"/>
-      <c r="J20" s="24"/>
-      <c r="K20" s="25"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="23"/>
       <c r="L20" s="1"/>
-      <c r="M20" s="28"/>
+      <c r="M20" s="26"/>
       <c r="N20" s="11"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.35">
@@ -2739,10 +3584,16 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="Q1:W1"/>
+  <mergeCells count="9">
     <mergeCell ref="H1:O1"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="Y1:AD1"/>
+    <mergeCell ref="AF1:AK1"/>
+    <mergeCell ref="AM1:AR1"/>
+    <mergeCell ref="AT1:AZ1"/>
+    <mergeCell ref="BB1:BH1"/>
+    <mergeCell ref="BJ1:BO1"/>
+    <mergeCell ref="Q1:W1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/tables/table-1.xlsx
+++ b/tables/table-1.xlsx
@@ -2,41 +2,31 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0574198c81a0fd8/ERP/moth-classification-research-project/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="582" documentId="8_{A016B768-059C-4773-BFB7-E0E6207DCD72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8DF23816-8081-4EF1-BE30-FE4B4A90417B}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CA260CDC-8A97-4DC1-B53B-CFAB535B8C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{4D26BEB4-BA8B-4CD5-932F-2328E7569F99}"/>
+    <workbookView xWindow="2085" yWindow="3555" windowWidth="21600" windowHeight="11295" xr2:uid="{4D26BEB4-BA8B-4CD5-932F-2328E7569F99}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="163">
   <si>
     <t>Species Name</t>
   </si>
@@ -522,6 +512,9 @@
   </si>
   <si>
     <t>+ 2.8%</t>
+  </si>
+  <si>
+    <t>encoder.layers[8,9,10,11] &amp; heads</t>
   </si>
 </sst>
 </file>
@@ -913,26 +906,26 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="3" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1451,144 +1444,144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE05A1F3-5367-4D87-8E13-238A620B94D7}">
   <dimension ref="A1:BO53"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="8" max="8" width="25.453125" customWidth="1"/>
-    <col min="9" max="9" width="19.08984375" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" customWidth="1"/>
-    <col min="11" max="11" width="20.6328125" customWidth="1"/>
-    <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" customWidth="1"/>
-    <col min="14" max="14" width="12.7265625" customWidth="1"/>
-    <col min="15" max="15" width="14.81640625" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="8" max="8" width="25.42578125" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" customWidth="1"/>
+    <col min="10" max="10" width="24.140625" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="21.85546875" customWidth="1"/>
+    <col min="13" max="13" width="26.140625" customWidth="1"/>
+    <col min="14" max="14" width="22.140625" customWidth="1"/>
+    <col min="15" max="15" width="20.42578125" customWidth="1"/>
     <col min="17" max="17" width="16" customWidth="1"/>
-    <col min="18" max="18" width="14.7265625" customWidth="1"/>
-    <col min="19" max="19" width="13.90625" customWidth="1"/>
-    <col min="20" max="20" width="28.36328125" customWidth="1"/>
-    <col min="21" max="21" width="16.1796875" customWidth="1"/>
-    <col min="22" max="22" width="17.26953125" customWidth="1"/>
-    <col min="23" max="23" width="12.1796875" customWidth="1"/>
-    <col min="25" max="25" width="16.54296875" customWidth="1"/>
-    <col min="26" max="26" width="21.54296875" customWidth="1"/>
-    <col min="27" max="27" width="18.7265625" customWidth="1"/>
-    <col min="28" max="28" width="18.90625" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" customWidth="1"/>
+    <col min="19" max="19" width="13.85546875" customWidth="1"/>
+    <col min="20" max="20" width="28.42578125" customWidth="1"/>
+    <col min="21" max="21" width="16.140625" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" customWidth="1"/>
+    <col min="25" max="25" width="16.5703125" customWidth="1"/>
+    <col min="26" max="26" width="21.5703125" customWidth="1"/>
+    <col min="27" max="27" width="18.7109375" customWidth="1"/>
+    <col min="28" max="28" width="18.85546875" customWidth="1"/>
     <col min="29" max="29" width="20" customWidth="1"/>
-    <col min="30" max="30" width="13.08984375" customWidth="1"/>
-    <col min="32" max="32" width="16.6328125" customWidth="1"/>
-    <col min="33" max="33" width="9.54296875" customWidth="1"/>
-    <col min="34" max="34" width="22.453125" customWidth="1"/>
-    <col min="35" max="35" width="14.453125" customWidth="1"/>
-    <col min="36" max="36" width="17.90625" customWidth="1"/>
-    <col min="37" max="37" width="13.453125" customWidth="1"/>
-    <col min="39" max="39" width="18.453125" customWidth="1"/>
-    <col min="40" max="40" width="22.26953125" customWidth="1"/>
-    <col min="41" max="41" width="20.453125" customWidth="1"/>
-    <col min="42" max="42" width="15.54296875" customWidth="1"/>
-    <col min="43" max="43" width="17.36328125" customWidth="1"/>
-    <col min="44" max="44" width="15.7265625" customWidth="1"/>
-    <col min="46" max="46" width="17.7265625" customWidth="1"/>
+    <col min="30" max="30" width="13.140625" customWidth="1"/>
+    <col min="32" max="32" width="16.5703125" customWidth="1"/>
+    <col min="33" max="33" width="9.5703125" customWidth="1"/>
+    <col min="34" max="34" width="22.42578125" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" customWidth="1"/>
+    <col min="36" max="36" width="17.85546875" customWidth="1"/>
+    <col min="37" max="37" width="13.42578125" customWidth="1"/>
+    <col min="39" max="39" width="18.42578125" customWidth="1"/>
+    <col min="40" max="40" width="22.28515625" customWidth="1"/>
+    <col min="41" max="41" width="20.42578125" customWidth="1"/>
+    <col min="42" max="42" width="15.5703125" customWidth="1"/>
+    <col min="43" max="43" width="17.42578125" customWidth="1"/>
+    <col min="44" max="44" width="15.7109375" customWidth="1"/>
+    <col min="46" max="46" width="17.7109375" customWidth="1"/>
     <col min="47" max="47" width="22" customWidth="1"/>
-    <col min="48" max="48" width="19.453125" customWidth="1"/>
-    <col min="49" max="49" width="34.453125" customWidth="1"/>
-    <col min="50" max="50" width="15.1796875" customWidth="1"/>
-    <col min="51" max="51" width="16.7265625" customWidth="1"/>
-    <col min="52" max="52" width="15.7265625" customWidth="1"/>
-    <col min="54" max="54" width="17.7265625" customWidth="1"/>
-    <col min="55" max="55" width="19.1796875" customWidth="1"/>
-    <col min="56" max="56" width="22.90625" customWidth="1"/>
-    <col min="57" max="57" width="21.90625" customWidth="1"/>
-    <col min="58" max="59" width="22.90625" customWidth="1"/>
-    <col min="60" max="60" width="15.81640625" customWidth="1"/>
-    <col min="62" max="62" width="25.453125" customWidth="1"/>
-    <col min="63" max="63" width="15.1796875" customWidth="1"/>
-    <col min="64" max="64" width="24.08984375" customWidth="1"/>
-    <col min="65" max="65" width="24.90625" customWidth="1"/>
-    <col min="66" max="66" width="22.453125" customWidth="1"/>
-    <col min="67" max="67" width="23.26953125" customWidth="1"/>
+    <col min="48" max="48" width="19.42578125" customWidth="1"/>
+    <col min="49" max="49" width="34.42578125" customWidth="1"/>
+    <col min="50" max="50" width="15.140625" customWidth="1"/>
+    <col min="51" max="51" width="16.7109375" customWidth="1"/>
+    <col min="52" max="52" width="15.7109375" customWidth="1"/>
+    <col min="54" max="54" width="17.7109375" customWidth="1"/>
+    <col min="55" max="55" width="19.140625" customWidth="1"/>
+    <col min="56" max="56" width="22.85546875" customWidth="1"/>
+    <col min="57" max="57" width="21.85546875" customWidth="1"/>
+    <col min="58" max="59" width="22.85546875" customWidth="1"/>
+    <col min="60" max="60" width="15.85546875" customWidth="1"/>
+    <col min="62" max="62" width="25.42578125" customWidth="1"/>
+    <col min="63" max="63" width="15.140625" customWidth="1"/>
+    <col min="64" max="64" width="24.140625" customWidth="1"/>
+    <col min="65" max="65" width="24.85546875" customWidth="1"/>
+    <col min="66" max="66" width="22.42578125" customWidth="1"/>
+    <col min="67" max="67" width="23.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:67" x14ac:dyDescent="0.35">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:67" x14ac:dyDescent="0.25">
+      <c r="A1" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="67"/>
-      <c r="C1" s="67"/>
-      <c r="D1" s="67"/>
-      <c r="E1" s="67"/>
-      <c r="F1" s="67"/>
-      <c r="H1" s="66" t="s">
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="H1" s="65" t="s">
         <v>72</v>
       </c>
-      <c r="I1" s="66"/>
-      <c r="J1" s="66"/>
-      <c r="K1" s="66"/>
-      <c r="L1" s="66"/>
-      <c r="M1" s="66"/>
-      <c r="N1" s="66"/>
-      <c r="O1" s="66"/>
-      <c r="Q1" s="65" t="s">
+      <c r="I1" s="65"/>
+      <c r="J1" s="65"/>
+      <c r="K1" s="65"/>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="Q1" s="64" t="s">
         <v>74</v>
       </c>
-      <c r="R1" s="65"/>
-      <c r="S1" s="65"/>
-      <c r="T1" s="65"/>
-      <c r="U1" s="65"/>
-      <c r="V1" s="65"/>
-      <c r="W1" s="65"/>
-      <c r="Y1" s="68" t="s">
+      <c r="R1" s="64"/>
+      <c r="S1" s="64"/>
+      <c r="T1" s="64"/>
+      <c r="U1" s="64"/>
+      <c r="V1" s="64"/>
+      <c r="W1" s="64"/>
+      <c r="Y1" s="67" t="s">
         <v>110</v>
       </c>
-      <c r="Z1" s="68"/>
-      <c r="AA1" s="68"/>
-      <c r="AB1" s="68"/>
-      <c r="AC1" s="68"/>
-      <c r="AD1" s="68"/>
-      <c r="AF1" s="62" t="s">
+      <c r="Z1" s="67"/>
+      <c r="AA1" s="67"/>
+      <c r="AB1" s="67"/>
+      <c r="AC1" s="67"/>
+      <c r="AD1" s="67"/>
+      <c r="AF1" s="68" t="s">
         <v>128</v>
       </c>
-      <c r="AG1" s="62"/>
-      <c r="AH1" s="62"/>
-      <c r="AI1" s="62"/>
-      <c r="AJ1" s="62"/>
-      <c r="AK1" s="62"/>
+      <c r="AG1" s="68"/>
+      <c r="AH1" s="68"/>
+      <c r="AI1" s="68"/>
+      <c r="AJ1" s="68"/>
+      <c r="AK1" s="68"/>
       <c r="AL1" s="39"/>
-      <c r="AM1" s="62" t="s">
+      <c r="AM1" s="68" t="s">
         <v>135</v>
       </c>
-      <c r="AN1" s="62"/>
-      <c r="AO1" s="62"/>
-      <c r="AP1" s="62"/>
-      <c r="AQ1" s="62"/>
-      <c r="AR1" s="62"/>
-      <c r="AT1" s="63" t="s">
+      <c r="AN1" s="68"/>
+      <c r="AO1" s="68"/>
+      <c r="AP1" s="68"/>
+      <c r="AQ1" s="68"/>
+      <c r="AR1" s="68"/>
+      <c r="AT1" s="62" t="s">
         <v>142</v>
       </c>
-      <c r="AU1" s="63"/>
-      <c r="AV1" s="63"/>
-      <c r="AW1" s="63"/>
-      <c r="AX1" s="63"/>
-      <c r="AY1" s="63"/>
-      <c r="AZ1" s="63"/>
-      <c r="BB1" s="63" t="s">
+      <c r="AU1" s="62"/>
+      <c r="AV1" s="62"/>
+      <c r="AW1" s="62"/>
+      <c r="AX1" s="62"/>
+      <c r="AY1" s="62"/>
+      <c r="AZ1" s="62"/>
+      <c r="BB1" s="62" t="s">
         <v>155</v>
       </c>
-      <c r="BC1" s="63"/>
-      <c r="BD1" s="63"/>
-      <c r="BE1" s="63"/>
-      <c r="BF1" s="63"/>
-      <c r="BG1" s="63"/>
-      <c r="BH1" s="63"/>
-      <c r="BJ1" s="64"/>
-      <c r="BK1" s="64"/>
-      <c r="BL1" s="64"/>
-      <c r="BM1" s="64"/>
-      <c r="BN1" s="64"/>
-      <c r="BO1" s="64"/>
-    </row>
-    <row r="2" spans="1:67" x14ac:dyDescent="0.35">
+      <c r="BC1" s="62"/>
+      <c r="BD1" s="62"/>
+      <c r="BE1" s="62"/>
+      <c r="BF1" s="62"/>
+      <c r="BG1" s="62"/>
+      <c r="BH1" s="62"/>
+      <c r="BJ1" s="63"/>
+      <c r="BK1" s="63"/>
+      <c r="BL1" s="63"/>
+      <c r="BM1" s="63"/>
+      <c r="BN1" s="63"/>
+      <c r="BO1" s="63"/>
+    </row>
+    <row r="2" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>55</v>
       </c>
@@ -1755,7 +1748,7 @@
       <c r="BN2" s="58"/>
       <c r="BO2" s="58"/>
     </row>
-    <row r="3" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1918,7 +1911,7 @@
       <c r="BJ3" s="40"/>
       <c r="BK3" s="46"/>
     </row>
-    <row r="4" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -2080,7 +2073,7 @@
       </c>
       <c r="BJ4" s="11"/>
     </row>
-    <row r="5" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -2208,7 +2201,7 @@
         <v>0.33100000000000002</v>
       </c>
       <c r="AW5" s="51" t="s">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="AX5" s="25">
         <v>1</v>
@@ -2242,7 +2235,7 @@
       </c>
       <c r="BJ5" s="11"/>
     </row>
-    <row r="6" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -2404,7 +2397,7 @@
       </c>
       <c r="BJ6" s="22"/>
     </row>
-    <row r="7" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -2475,7 +2468,7 @@
       <c r="AC7" s="34"/>
       <c r="AD7" s="34"/>
     </row>
-    <row r="8" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -2540,7 +2533,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -2605,7 +2598,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -2649,7 +2642,7 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="11" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -2669,7 +2662,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="12" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -2697,7 +2690,7 @@
       <c r="N12" s="11"/>
       <c r="O12" s="11"/>
     </row>
-    <row r="13" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -2725,7 +2718,7 @@
       <c r="N13" s="11"/>
       <c r="O13" s="11"/>
     </row>
-    <row r="14" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -2753,7 +2746,7 @@
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
     </row>
-    <row r="15" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -2781,7 +2774,7 @@
       <c r="N15" s="11"/>
       <c r="O15" s="11"/>
     </row>
-    <row r="16" spans="1:67" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -2809,7 +2802,7 @@
       <c r="N16" s="11"/>
       <c r="O16" s="11"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -2837,7 +2830,7 @@
       <c r="N17" s="11"/>
       <c r="O17" s="11"/>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -2864,7 +2857,7 @@
       <c r="M18" s="26"/>
       <c r="N18" s="11"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -2891,7 +2884,7 @@
       <c r="M19" s="26"/>
       <c r="N19" s="11"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -2918,7 +2911,7 @@
       <c r="M20" s="26"/>
       <c r="N20" s="11"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -2945,7 +2938,7 @@
       <c r="M21" s="8"/>
       <c r="N21" s="8"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -2965,7 +2958,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -2985,7 +2978,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -3005,7 +2998,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -3025,7 +3018,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -3045,7 +3038,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -3065,7 +3058,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -3085,7 +3078,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -3105,7 +3098,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -3125,7 +3118,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -3145,7 +3138,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -3165,7 +3158,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -3185,7 +3178,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -3205,7 +3198,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -3225,7 +3218,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -3245,7 +3238,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -3265,7 +3258,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -3285,7 +3278,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -3305,7 +3298,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -3325,7 +3318,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -3345,7 +3338,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -3365,7 +3358,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -3385,7 +3378,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -3405,7 +3398,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -3425,7 +3418,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -3445,7 +3438,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -3465,7 +3458,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -3485,7 +3478,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -3505,7 +3498,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -3525,7 +3518,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -3545,7 +3538,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>50</v>
       </c>
@@ -3565,7 +3558,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="4" t="s">
         <v>4</v>
@@ -3585,7 +3578,6 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="H1:O1"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="Y1:AD1"/>
     <mergeCell ref="AF1:AK1"/>
@@ -3594,6 +3586,7 @@
     <mergeCell ref="BB1:BH1"/>
     <mergeCell ref="BJ1:BO1"/>
     <mergeCell ref="Q1:W1"/>
+    <mergeCell ref="H1:O1"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
